--- a/tracking_forms/031_microdermabrasion_treatment_record_form--tracking_forms.xlsx
+++ b/tracking_forms/031_microdermabrasion_treatment_record_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_id</t>
+          <t>Microdermabrasion Session ID</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>client_address</t>
+          <t>Client Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>practitioner_name</t>
+          <t>Practitioner Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_start_date</t>
+          <t>Microdermabrasion Session Start Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_duration</t>
+          <t>Microdermabrasion Session Duration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_end_date</t>
+          <t>Microdermabrasion Session End Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_notes</t>
+          <t>Microdermabrasion Session Notes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>microdermabrasion_next_session</t>
+          <t>Microdermabrasion Next Session</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>microdermabrasion_treatment_outcome</t>
+          <t>Microdermabrasion Treatment Outcome</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>microdermabrasion_side_effects</t>
+          <t>Microdermabrasion Side Effects</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_photo</t>
+          <t>Microdermabrasion Session Photo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>microdermabrasion_next_session_notes</t>
+          <t>Microdermabrasion Next Session Notes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>microdermabrasion_treatment_outcome_notes</t>
+          <t>Microdermabrasion Treatment Outcome Notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,13 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>practitioner_signature</t>
+          <t>Practitioner Signature</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>practitioner_name_label</t>
+          <t>microdermabrasion_session_id_label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>practitioner_name</t>
+          <t>Microdermabrasion Session ID Label</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_id_label</t>
+          <t>microdermabrasion_session_start_date_label</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_id</t>
+          <t>Microdermabrasion Session Start Date Label</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_start_date_label</t>
+          <t>microdermabrasion_session_duration_label</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_start_date</t>
+          <t>Microdermabrasion Session Duration Label</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>microdermabrasion_treatment_outcome</t>
+          <t>Microdermabrasion Treatment Outcome Label</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_end_date</t>
+          <t>Microdermabrasion Session End Date Label</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_duration_label</t>
+          <t>microdermabrasion_session_notes_label</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_duration</t>
+          <t>Microdermabrasion Session Notes Label</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_notes_label</t>
+          <t>microdermabrasion_treatment_outcome_notes_label</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>microdermabrasion_session_notes</t>
+          <t>Microdermabrasion Treatment Outcome Notes Label</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>microdermabrasion_treatment_outcome_notes_label</t>
+          <t>microdermabrasion_next_session_label</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>microdermabrasion_treatment_outcome_notes</t>
+          <t>Microdermabrasion Next Session Label</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>microdermabrasion_next_session_label</t>
+          <t>microdermabrasion_next_session_notes_label</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>microdermabrasion_next_session</t>
+          <t>Microdermabrasion Next Session Notes Label</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>microdermabrasion_next_session_notes_label</t>
+          <t>microdermabrasion_treatment_outcome_notes_label_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>microdermabrasion_next_session_notes</t>
+          <t>Microdermabrasion Treatment Outcome Notes Label 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
